--- a/imports/Consumo.xlsx
+++ b/imports/Consumo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14E4ACB-D872-4B6A-AEC5-54D17AA6006A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F73BA7F-F0D5-4FC2-A934-53F55D2173F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>BD</t>
   </si>
@@ -177,6 +177,15 @@
   </si>
   <si>
     <t>x m2 = 2 mL</t>
+  </si>
+  <si>
+    <t>CM-DS-009</t>
+  </si>
+  <si>
+    <t>= 8 mL</t>
+  </si>
+  <si>
+    <t>009</t>
   </si>
 </sst>
 </file>
@@ -306,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -344,6 +353,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
@@ -733,11 +745,11 @@
         <v>46</v>
       </c>
       <c r="E4" s="2" t="str">
-        <f t="shared" ref="E4:E10" si="0">"CM"</f>
+        <f t="shared" ref="E4:E11" si="0">"CM"</f>
         <v>CM</v>
       </c>
       <c r="F4" s="2" t="str">
-        <f t="shared" ref="F4:F10" si="1">"DS"</f>
+        <f t="shared" ref="F4:F11" si="1">"DS"</f>
         <v>DS</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -934,6 +946,43 @@
         <v>44</v>
       </c>
     </row>
+    <row r="11" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="14">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>CM</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DS</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="13" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="14" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="15" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="16" spans="1:9" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
